--- a/artfynd/A 5750-2023 artfynd.xlsx
+++ b/artfynd/A 5750-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 5750-2023 artfynd.xlsx
+++ b/artfynd/A 5750-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,60 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55905073</v>
+        <v>109337100</v>
       </c>
       <c r="B2" t="n">
-        <v>5413</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101920</v>
+        <v>6463</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>hygge vid Nässelbopuss (#79), Upl</t>
+          <t>Nässelbopussen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>630442.2244333401</v>
+        <v>630578</v>
       </c>
       <c r="R2" t="n">
-        <v>6649482.217028236</v>
+        <v>6649702</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,27 +747,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-11-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-11-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>inventering ÅGP-insekter på tall</t>
+          <t>2023-05-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,38 +761,58 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>tallåga med 3 nya flyghål</t>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Våtmark</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Stor sälg som nog har legat omkull en längre tid av påväxten att döma. # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Thorleif Joelson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Thorleif Joelson, Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>55905072</v>
       </c>
       <c r="B3" t="n">
-        <v>5413</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -857,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>630767.9644556947</v>
+        <v>630768</v>
       </c>
       <c r="R3" t="n">
-        <v>6649669.15441101</v>
+        <v>6649669</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,19 +887,9 @@
           <t>2015-11-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-11-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -936,6 +923,123 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>55905073</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5482</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>101920</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Raggbock</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tragosoma depsarium</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1767)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>hygge vid Nässelbopuss (#79), Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>630442</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6649482</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2015-11-14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2015-11-14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>inventering ÅGP-insekter på tall</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>tallåga med 3 nya flyghål</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
